--- a/output/yearly_surface_area_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_21_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641916064</v>
+        <v>10.84497654078669</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907224486937</v>
+        <v>37.78907266867258</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.542947538177491</v>
+        <v>5.874778262212914</v>
       </c>
       <c r="C2" t="n">
-        <v>10.17483320681394</v>
+        <v>7.449501579824798</v>
       </c>
       <c r="D2" t="n">
-        <v>23.63950297055895</v>
+        <v>26.04478484596363</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.85522542358599</v>
+        <v>18.4666743168825</v>
       </c>
       <c r="C3" t="n">
-        <v>23.12015843501239</v>
+        <v>18.20160243673586</v>
       </c>
       <c r="D3" t="n">
-        <v>71.42705422247668</v>
+        <v>79.8602670019568</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.82120841130262</v>
+        <v>34.15303913533804</v>
       </c>
       <c r="C4" t="n">
-        <v>47.00509833163304</v>
+        <v>53.37369568908209</v>
       </c>
       <c r="D4" t="n">
-        <v>100.8254892261474</v>
+        <v>95.52896036173588</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.06788912697583</v>
+        <v>41.42975311921541</v>
       </c>
       <c r="C5" t="n">
-        <v>84.97026380256145</v>
+        <v>96.94758579437256</v>
       </c>
       <c r="D5" t="n">
-        <v>76.79721416470676</v>
+        <v>63.93631923907354</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.04410619789565</v>
+        <v>40.8151790563569</v>
       </c>
       <c r="C6" t="n">
-        <v>103.4467555964864</v>
+        <v>114.9184775206104</v>
       </c>
       <c r="D6" t="n">
-        <v>51.84413276586557</v>
+        <v>44.11581483803468</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.78738702100172</v>
+        <v>29.88341836956866</v>
       </c>
       <c r="C7" t="n">
-        <v>93.6626579759627</v>
+        <v>105.6998665777328</v>
       </c>
       <c r="D7" t="n">
-        <v>40.24380189248525</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C8" t="n">
-        <v>57.66295140893641</v>
+        <v>73.51817683252239</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>43.04374634499714</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.701245897685473</v>
+        <v>7.691726952932148</v>
       </c>
       <c r="C21" t="n">
-        <v>94.34026224664704</v>
+        <v>94.22365517341882</v>
       </c>
       <c r="D21" t="n">
-        <v>8.663901634896158</v>
+        <v>8.653192822048668</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.39648720379547</v>
+        <v>6.219371706403543</v>
       </c>
       <c r="C2" t="n">
-        <v>8.769952242036757</v>
+        <v>9.371763584740052</v>
       </c>
       <c r="D2" t="n">
-        <v>23.67288239250334</v>
+        <v>25.80131141531043</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.22967220953152</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="C3" t="n">
-        <v>32.03933632809466</v>
+        <v>23.75829444277281</v>
       </c>
       <c r="D3" t="n">
-        <v>73.93051086830606</v>
+        <v>81.34270603536947</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.80469862677967</v>
+        <v>34.34447993766616</v>
       </c>
       <c r="C4" t="n">
-        <v>51.98255919216436</v>
+        <v>49.28962523941536</v>
       </c>
       <c r="D4" t="n">
-        <v>110.6400210255028</v>
+        <v>110.0018850177424</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.58392856651115</v>
+        <v>46.28940425523712</v>
       </c>
       <c r="C5" t="n">
-        <v>85.80474935117124</v>
+        <v>96.67760517570468</v>
       </c>
       <c r="D5" t="n">
-        <v>93.56055621472105</v>
+        <v>81.53414683769762</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.49695393146069</v>
+        <v>47.85921883432777</v>
       </c>
       <c r="C6" t="n">
-        <v>117.9373517111694</v>
+        <v>134.0782657166912</v>
       </c>
       <c r="D6" t="n">
-        <v>61.98755004614362</v>
+        <v>52.40765594810324</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.83026512481909</v>
+        <v>38.68675003354981</v>
       </c>
       <c r="C7" t="n">
-        <v>121.3302717770463</v>
+        <v>134.026233088366</v>
       </c>
       <c r="D7" t="n">
-        <v>45.57371017884118</v>
+        <v>42.4596064609703</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.44766125760332</v>
+        <v>23.78283813537898</v>
       </c>
       <c r="C8" t="n">
-        <v>89.12305659152544</v>
+        <v>105.9796646734432</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.20468654856884</v>
+        <v>12.09218647320796</v>
       </c>
       <c r="C9" t="n">
-        <v>52.36249555370786</v>
+        <v>65.56405693271472</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>35.16129402759952</v>
+        <v>40.9977841293468</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
         <v>37.13853390395258</v>
@@ -1237,7 +1237,7 @@
         <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.888447852119204</v>
+        <v>7.874950570800553</v>
       </c>
       <c r="C21" t="n">
-        <v>103.5358780590646</v>
+        <v>103.3587262417573</v>
       </c>
       <c r="D21" t="n">
-        <v>9.860559815149005</v>
+        <v>9.843688213500691</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.597745483166066</v>
+        <v>6.497206306705391</v>
       </c>
       <c r="C2" t="n">
-        <v>9.513135254151592</v>
+        <v>14.90685714128357</v>
       </c>
       <c r="D2" t="n">
-        <v>26.83607349558656</v>
+        <v>36.56224800155971</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.48907458763093</v>
+        <v>19.57114048416017</v>
       </c>
       <c r="C3" t="n">
-        <v>32.78546458332223</v>
+        <v>29.55551463635023</v>
       </c>
       <c r="D3" t="n">
-        <v>74.76499641691585</v>
+        <v>82.10356050616076</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.67707142522758</v>
+        <v>34.8422260237193</v>
       </c>
       <c r="C4" t="n">
-        <v>64.52831310473435</v>
+        <v>53.29711936815084</v>
       </c>
       <c r="D4" t="n">
-        <v>118.7443483240602</v>
+        <v>122.2413336465873</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.90299657039137</v>
+        <v>48.17926858591223</v>
       </c>
       <c r="C5" t="n">
-        <v>90.27170140549423</v>
+        <v>92.89787651435444</v>
       </c>
       <c r="D5" t="n">
-        <v>109.0230825566083</v>
+        <v>96.97212948697872</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.17872880656449</v>
+        <v>53.97747052719389</v>
       </c>
       <c r="C6" t="n">
-        <v>125.3034047361332</v>
+        <v>143.1751399442421</v>
       </c>
       <c r="D6" t="n">
-        <v>73.70078190551232</v>
+        <v>63.3963580017378</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.93302983859552</v>
+        <v>46.59178254814513</v>
       </c>
       <c r="C7" t="n">
-        <v>142.8894513623063</v>
+        <v>159.5978155408827</v>
       </c>
       <c r="D7" t="n">
-        <v>51.92169083450106</v>
+        <v>46.47200932822701</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.95803119509142</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="C8" t="n">
-        <v>121.9183386518901</v>
+        <v>138.357703959503</v>
       </c>
       <c r="D8" t="n">
-        <v>41.47393176590651</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.08593613408398</v>
+        <v>17.30624853046277</v>
       </c>
       <c r="C9" t="n">
-        <v>77.65624340592267</v>
+        <v>93.63124204942677</v>
       </c>
       <c r="D9" t="n">
-        <v>37.60780930658255</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>47.26133448244146</v>
+        <v>56.51430659496764</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>36.25005223160922</v>
+        <v>39.44858625204532</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.060911590921705</v>
+        <v>8.043306250684251</v>
       </c>
       <c r="C21" t="n">
-        <v>111.8451483240387</v>
+        <v>111.600874228244</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08375343751734</v>
+        <v>11.05954609469084</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.924266558052754</v>
+        <v>6.039711876526377</v>
       </c>
       <c r="C2" t="n">
-        <v>6.316564729123979</v>
+        <v>10.01677182643021</v>
       </c>
       <c r="D2" t="n">
-        <v>21.82817845622358</v>
+        <v>29.87949137875167</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.64539345678443</v>
+        <v>23.92028281397354</v>
       </c>
       <c r="C3" t="n">
-        <v>47.70802968787375</v>
+        <v>46.17650326924873</v>
       </c>
       <c r="D3" t="n">
-        <v>83.5663645854885</v>
+        <v>89.65810909033996</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.52620107394306</v>
+        <v>23.13881164139307</v>
       </c>
       <c r="C4" t="n">
-        <v>81.60483267240336</v>
+        <v>76.04028668473245</v>
       </c>
       <c r="D4" t="n">
-        <v>117.2893982263664</v>
+        <v>115.3367020426195</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.50780990946964</v>
+        <v>30.40963513904496</v>
       </c>
       <c r="C5" t="n">
-        <v>74.8582624488193</v>
+        <v>85.53476873250337</v>
       </c>
       <c r="D5" t="n">
-        <v>74.39193228930206</v>
+        <v>64.86897955810801</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.49817235887642</v>
+        <v>28.90068891761761</v>
       </c>
       <c r="C6" t="n">
-        <v>94.10837143369076</v>
+        <v>105.0970734873253</v>
       </c>
       <c r="D6" t="n">
-        <v>34.17365583712723</v>
+        <v>30.59125846433062</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.82246789644735</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>85.69773885140832</v>
+        <v>97.25585457350601</v>
       </c>
       <c r="D7" t="n">
-        <v>29.16477905005999</v>
+        <v>28.38625312059227</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="C8" t="n">
-        <v>57.24570863463151</v>
+        <v>69.01195487002953</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>36.0546844384641</v>
+        <v>43.15468383557703</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.32833000604172</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.18911745402114</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C2" t="n">
-        <v>3.148464887519521</v>
+        <v>4.300054944601029</v>
       </c>
       <c r="D2" t="n">
-        <v>15.29072049364407</v>
+        <v>21.86646661668921</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.45042657426681</v>
+        <v>23.14961086613979</v>
       </c>
       <c r="C3" t="n">
-        <v>36.29030388748335</v>
+        <v>43.44233591292136</v>
       </c>
       <c r="D3" t="n">
-        <v>83.10003442597127</v>
+        <v>92.61807841864409</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.53217367562655</v>
+        <v>33.32346232524949</v>
       </c>
       <c r="C4" t="n">
-        <v>103.4035586974995</v>
+        <v>98.0815043927776</v>
       </c>
       <c r="D4" t="n">
-        <v>131.3283903970958</v>
+        <v>132.132441766874</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.55122779263475</v>
+        <v>33.62485887045326</v>
       </c>
       <c r="C5" t="n">
-        <v>111.5510828950438</v>
+        <v>112.9009859883832</v>
       </c>
       <c r="D5" t="n">
-        <v>92.40700266223104</v>
+        <v>83.71853547964676</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.49566908412018</v>
+        <v>34.57617239586842</v>
       </c>
       <c r="C6" t="n">
-        <v>109.0819874188631</v>
+        <v>122.6065437925672</v>
       </c>
       <c r="D6" t="n">
-        <v>43.19002675292993</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="C7" t="n">
-        <v>108.6343104657265</v>
+        <v>121.9890244865959</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>75.93818492349078</v>
+        <v>89.70719647555229</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>42.71093387325747</v>
+        <v>49.47812079863073</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.411393345808419</v>
+        <v>3.463605900582747</v>
       </c>
       <c r="C2" t="n">
-        <v>10.84634863651876</v>
+        <v>9.116509181635882</v>
       </c>
       <c r="D2" t="n">
-        <v>15.53026693348029</v>
+        <v>19.20200334736336</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.24225500323749</v>
+        <v>17.87762569433442</v>
       </c>
       <c r="C3" t="n">
-        <v>23.04652735719387</v>
+        <v>28.96155727528091</v>
       </c>
       <c r="D3" t="n">
-        <v>76.42415003709296</v>
+        <v>89.54029936583034</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.90902592533709</v>
+        <v>38.84972015245478</v>
       </c>
       <c r="C4" t="n">
-        <v>97.63480918734528</v>
+        <v>104.3990508696058</v>
       </c>
       <c r="D4" t="n">
-        <v>141.9724990065397</v>
+        <v>145.8396032135679</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.84070449666732</v>
+        <v>41.15977250054753</v>
       </c>
       <c r="C5" t="n">
-        <v>151.1155153761903</v>
+        <v>146.1576894697439</v>
       </c>
       <c r="D5" t="n">
-        <v>115.7235106380928</v>
+        <v>106.519625910779</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.80888765950392</v>
+        <v>39.72838434775569</v>
       </c>
       <c r="C6" t="n">
-        <v>143.0946366324939</v>
+        <v>149.6154048841012</v>
       </c>
       <c r="D6" t="n">
-        <v>59.25043744670351</v>
+        <v>53.01143078621504</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.26647990067416</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="C7" t="n">
-        <v>132.2296347895944</v>
+        <v>149.7764115075976</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>108.3996727644116</v>
+        <v>123.5873097491097</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>66.34061936677394</v>
+        <v>76.99061846244334</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>40.28601704376787</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
         <v>30.7483380970101</v>
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>11.33329549782518</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.149446635223768</v>
+        <v>2.076396394482004</v>
       </c>
       <c r="C2" t="n">
-        <v>4.902848035008571</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="D2" t="n">
-        <v>10.69515949006475</v>
+        <v>13.2506487642192</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.42526098685489</v>
+        <v>17.11677122354314</v>
       </c>
       <c r="C3" t="n">
-        <v>33.24688600431823</v>
+        <v>33.74757733348411</v>
       </c>
       <c r="D3" t="n">
-        <v>74.72572650874598</v>
+        <v>88.11185645615123</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.1207235765559</v>
+        <v>42.58919715793088</v>
       </c>
       <c r="C4" t="n">
-        <v>92.87431456945251</v>
+        <v>103.4673722982756</v>
       </c>
       <c r="D4" t="n">
-        <v>149.9109109430794</v>
+        <v>158.6788996897077</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.90237467558562</v>
+        <v>42.95146206079796</v>
       </c>
       <c r="C5" t="n">
-        <v>179.7825483401972</v>
+        <v>178.751713250738</v>
       </c>
       <c r="D5" t="n">
-        <v>125.0992012136498</v>
+        <v>112.7782675253524</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.09315252537899</v>
+        <v>33.93214590188251</v>
       </c>
       <c r="C6" t="n">
-        <v>178.2745838664741</v>
+        <v>184.6343454945849</v>
       </c>
       <c r="D6" t="n">
-        <v>58.00263611460582</v>
+        <v>51.92463607761381</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>140.434100353985</v>
+        <v>158.8791762213741</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>83.94924619014475</v>
+        <v>95.46514676095984</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>33.39218466454675</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.506263020221864</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.16417285078747</v>
+        <v>2.794053966286422</v>
       </c>
       <c r="C2" t="n">
-        <v>4.473824288252715</v>
+        <v>8.229009256996765</v>
       </c>
       <c r="D2" t="n">
-        <v>9.401216015867456</v>
+        <v>16.38242394076652</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.7275982220339</v>
+        <v>12.2963899956913</v>
       </c>
       <c r="C3" t="n">
-        <v>25.95740930028567</v>
+        <v>24.71058971589222</v>
       </c>
       <c r="D3" t="n">
-        <v>66.81284001251667</v>
+        <v>79.21722225567514</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.77238306799753</v>
+        <v>38.00738062221102</v>
       </c>
       <c r="C4" t="n">
-        <v>87.84580282830034</v>
+        <v>94.75043443226816</v>
       </c>
       <c r="D4" t="n">
-        <v>152.5910821756733</v>
+        <v>165.3410396107266</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.28435664799564</v>
+        <v>52.10625940289948</v>
       </c>
       <c r="C5" t="n">
-        <v>177.2054606165493</v>
+        <v>185.8693841065274</v>
       </c>
       <c r="D5" t="n">
-        <v>146.3540390105933</v>
+        <v>139.972678932989</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.11581483803468</v>
+        <v>43.71329827929349</v>
       </c>
       <c r="C6" t="n">
-        <v>228.6696570208714</v>
+        <v>230.561484846955</v>
       </c>
       <c r="D6" t="n">
-        <v>78.97374882502193</v>
+        <v>69.11209313586272</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.58292145661112</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>194.451822537053</v>
+        <v>208.465289267472</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>40.18391528252619</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>127.0921490532708</v>
+        <v>142.9473744768568</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>58.46405753560178</v>
+        <v>64.5656195174957</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.331650797586175</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C2" t="n">
-        <v>3.556871932486194</v>
+        <v>4.387430490278995</v>
       </c>
       <c r="D2" t="n">
-        <v>8.116108271008383</v>
+        <v>12.56244362354219</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.79846398318892</v>
+        <v>11.24101121362598</v>
       </c>
       <c r="C3" t="n">
-        <v>22.43293504203962</v>
+        <v>28.56885819358218</v>
       </c>
       <c r="D3" t="n">
-        <v>60.79963532400497</v>
+        <v>75.22641783791185</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.19882142453914</v>
+        <v>33.09373336245573</v>
       </c>
       <c r="C4" t="n">
-        <v>79.29478032431062</v>
+        <v>82.29401956078463</v>
       </c>
       <c r="D4" t="n">
-        <v>152.2464887314826</v>
+        <v>167.3575493952495</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.07037670619884</v>
+        <v>56.20505606812991</v>
       </c>
       <c r="C5" t="n">
-        <v>177.2054606165493</v>
+        <v>187.7837921298087</v>
       </c>
       <c r="D5" t="n">
-        <v>161.6447595042374</v>
+        <v>158.8958659323463</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.48815925985148</v>
+        <v>51.20010627187966</v>
       </c>
       <c r="C6" t="n">
-        <v>257.892359185482</v>
+        <v>263.0848227932433</v>
       </c>
       <c r="D6" t="n">
-        <v>93.46434493970486</v>
+        <v>83.48193428292329</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>18.20552942755285</v>
       </c>
       <c r="C7" t="n">
-        <v>244.8164615126186</v>
+        <v>255.5960513052486</v>
       </c>
       <c r="D7" t="n">
-        <v>48.02906118716245</v>
+        <v>45.6934833987593</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>163.8929617469625</v>
+        <v>180.9999154934632</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>69.89061906533041</v>
+        <v>74.77186865084555</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
         <v>25.19655482949439</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.312416754128738</v>
+        <v>2.837250865273282</v>
       </c>
       <c r="C2" t="n">
-        <v>12.4495426375538</v>
+        <v>5.358378969779091</v>
       </c>
       <c r="D2" t="n">
-        <v>14.94023656322796</v>
+        <v>17.56739341979242</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.94648690235194</v>
+        <v>9.184249773228911</v>
       </c>
       <c r="C3" t="n">
-        <v>18.38813450054276</v>
+        <v>23.25269437508571</v>
       </c>
       <c r="D3" t="n">
-        <v>54.48208884717674</v>
+        <v>68.91868883812609</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.78742807873073</v>
+        <v>27.84825537866502</v>
       </c>
       <c r="C4" t="n">
-        <v>68.57409539393547</v>
+        <v>77.18893149870122</v>
       </c>
       <c r="D4" t="n">
-        <v>148.4559608453857</v>
+        <v>166.3237690626776</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.75130870231863</v>
+        <v>53.72614311490671</v>
       </c>
       <c r="C5" t="n">
-        <v>163.3137306014569</v>
+        <v>171.9531103988289</v>
       </c>
       <c r="D5" t="n">
-        <v>172.7875959474387</v>
+        <v>175.9537322936346</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.59132488425541</v>
+        <v>60.45798712292709</v>
       </c>
       <c r="C6" t="n">
-        <v>268.5187963362494</v>
+        <v>278.0986904342898</v>
       </c>
       <c r="D6" t="n">
-        <v>115.2807424234775</v>
+        <v>104.4932986492135</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.53650157707104</v>
+        <v>32.27888276793088</v>
       </c>
       <c r="C7" t="n">
-        <v>297.7562247164236</v>
+        <v>306.0205768907733</v>
       </c>
       <c r="D7" t="n">
-        <v>59.10808402958771</v>
+        <v>53.95783557310894</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>229.6504229774139</v>
+        <v>244.4208171878071</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>119.8124898262807</v>
+        <v>129.0203015444115</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>51.53193699591508</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.443791020048564</v>
+        <v>6.704355072301468</v>
       </c>
       <c r="C2" t="n">
-        <v>4.468915549731481</v>
+        <v>7.454410318346032</v>
       </c>
       <c r="D2" t="n">
-        <v>16.90667721483432</v>
+        <v>6.439283192154829</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.371902453460294</v>
+        <v>2.030254252382404</v>
       </c>
       <c r="C2" t="n">
-        <v>7.070546965985528</v>
+        <v>3.086614782151972</v>
       </c>
       <c r="D2" t="n">
-        <v>10.99655603526852</v>
+        <v>12.92863551722625</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.75566799482956</v>
+        <v>12.53691818323177</v>
       </c>
       <c r="C3" t="n">
-        <v>30.14947199741955</v>
+        <v>26.08994524035899</v>
       </c>
       <c r="D3" t="n">
-        <v>60.91744504851459</v>
+        <v>76.08053834060657</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.50360518121217</v>
+        <v>39.74311056331938</v>
       </c>
       <c r="C4" t="n">
-        <v>96.95838501911925</v>
+        <v>108.2278669161684</v>
       </c>
       <c r="D4" t="n">
-        <v>153.2419809035889</v>
+        <v>170.44612767281</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.86462629446773</v>
+        <v>35.53926689373454</v>
       </c>
       <c r="C5" t="n">
-        <v>233.3614292994669</v>
+        <v>243.5225180384214</v>
       </c>
       <c r="D5" t="n">
-        <v>160.4912059517474</v>
+        <v>157.8895745354933</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.81010608691964</v>
+        <v>20.04532462531138</v>
       </c>
       <c r="C6" t="n">
-        <v>251.3715909338746</v>
+        <v>256.0407830152724</v>
       </c>
       <c r="D6" t="n">
-        <v>90.32471578152357</v>
+        <v>82.11337798320324</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.407867265618931</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>161.4543004496134</v>
+        <v>171.8745705824891</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>88.28857104291565</v>
+        <v>95.04790398665493</v>
       </c>
       <c r="D8" t="n">
-        <v>25.36836067773758</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>39.2718716652809</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.231152678854506</v>
+        <v>6.404922022506191</v>
       </c>
       <c r="C2" t="n">
-        <v>3.675663404700058</v>
+        <v>6.180101798233672</v>
       </c>
       <c r="D2" t="n">
-        <v>18.64142540823844</v>
+        <v>15.87976911619216</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.56498795602743</v>
+        <v>14.24025045009999</v>
       </c>
       <c r="C3" t="n">
-        <v>11.26064616771092</v>
+        <v>18.78083358224148</v>
       </c>
       <c r="D3" t="n">
-        <v>17.33766445699867</v>
+        <v>8.546113765468485</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39739824799555</v>
+        <v>13.39846600589229</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13932023950612</v>
+        <v>70.14491026614196</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576164499764182</v>
+        <v>1.576290118340269</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.929936060099982</v>
+        <v>4.123340357836604</v>
       </c>
       <c r="C2" t="n">
-        <v>9.015389168098459</v>
+        <v>3.867104207028186</v>
       </c>
       <c r="D2" t="n">
-        <v>15.29661097986955</v>
+        <v>20.28683456055609</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.53892273636927</v>
+        <v>19.00663555421825</v>
       </c>
       <c r="C3" t="n">
-        <v>13.17996292951343</v>
+        <v>22.10895829963817</v>
       </c>
       <c r="D3" t="n">
-        <v>28.80447764260142</v>
+        <v>19.81657741022187</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.49019520405542</v>
+        <v>16.51495988083984</v>
       </c>
       <c r="C4" t="n">
-        <v>17.71465557542945</v>
+        <v>29.1628155546515</v>
       </c>
       <c r="D4" t="n">
-        <v>24.15982925380975</v>
+        <v>19.55248727777947</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44048148496637</v>
+        <v>15.44140988897479</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14163354770714</v>
+        <v>86.14681306480672</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250627681045553</v>
+        <v>3.250823134521008</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.837070938824034</v>
+        <v>4.713370728088937</v>
       </c>
       <c r="C2" t="n">
-        <v>4.766385104118264</v>
+        <v>6.669012154948583</v>
       </c>
       <c r="D2" t="n">
-        <v>29.45439462281281</v>
+        <v>19.21083907670159</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.32017292477148</v>
+        <v>16.33628179866693</v>
       </c>
       <c r="C3" t="n">
-        <v>26.46300936797277</v>
+        <v>17.82362957060084</v>
       </c>
       <c r="D3" t="n">
-        <v>34.35626091011713</v>
+        <v>31.44537896702533</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.00216878405352</v>
+        <v>28.07798434145878</v>
       </c>
       <c r="C4" t="n">
-        <v>26.71237328485147</v>
+        <v>44.59294422229862</v>
       </c>
       <c r="D4" t="n">
-        <v>33.15754696323177</v>
+        <v>25.09150782513998</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.14912784005428</v>
+        <v>14.23534171157875</v>
       </c>
       <c r="C5" t="n">
-        <v>20.91122610045706</v>
+        <v>32.98672286269284</v>
       </c>
       <c r="D5" t="n">
-        <v>31.09685853201772</v>
+        <v>29.47697482001049</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5280,7 +5280,7 @@
         <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73634445974862</v>
+        <v>16.73506455830615</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0917012044666</v>
+        <v>102.0838938056675</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020903337924586</v>
+        <v>5.020519367491844</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.407466354991432</v>
+        <v>5.014767273292708</v>
       </c>
       <c r="C2" t="n">
-        <v>4.405101948955438</v>
+        <v>7.067601722872788</v>
       </c>
       <c r="D2" t="n">
-        <v>30.70906818884023</v>
+        <v>25.64325003492669</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.00739631774425</v>
+        <v>16.23319828972101</v>
       </c>
       <c r="C3" t="n">
-        <v>21.853703896534</v>
+        <v>22.46238747316702</v>
       </c>
       <c r="D3" t="n">
-        <v>49.09720268938299</v>
+        <v>39.04901493641688</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.6568145763369</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="C4" t="n">
-        <v>48.52386203010285</v>
+        <v>44.59294422229862</v>
       </c>
       <c r="D4" t="n">
-        <v>42.38499363544754</v>
+        <v>34.66354794154638</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.71549845441346</v>
+        <v>28.05344064885261</v>
       </c>
       <c r="C5" t="n">
-        <v>36.54555829058752</v>
+        <v>59.32210502911353</v>
       </c>
       <c r="D5" t="n">
-        <v>35.4901795085222</v>
+        <v>31.53864499892879</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.27046364475338</v>
+        <v>12.67927160034756</v>
       </c>
       <c r="C6" t="n">
-        <v>23.26545709524092</v>
+        <v>33.2881194078966</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5591,7 +5591,7 @@
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06463596117861</v>
+        <v>18.06210526259669</v>
       </c>
       <c r="C21" t="n">
-        <v>117.850244127689</v>
+        <v>117.8337343321784</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881766080448993</v>
+        <v>6.880802004798739</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.60479764354504</v>
+        <v>5.69119144151876</v>
       </c>
       <c r="C2" t="n">
-        <v>5.940555358397449</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="D2" t="n">
-        <v>27.625398649801</v>
+        <v>33.81531792507713</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.72268948351267</v>
+        <v>14.91765636603028</v>
       </c>
       <c r="C3" t="n">
-        <v>17.97089172623786</v>
+        <v>23.78774687390022</v>
       </c>
       <c r="D3" t="n">
-        <v>57.86911842682824</v>
+        <v>46.89808783187013</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.35203081966388</v>
+        <v>22.32199755145973</v>
       </c>
       <c r="C4" t="n">
-        <v>43.12523140444964</v>
+        <v>42.42328179591317</v>
       </c>
       <c r="D4" t="n">
-        <v>49.07265899677682</v>
+        <v>39.96007680595792</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.34672117051515</v>
+        <v>22.67837196810132</v>
       </c>
       <c r="C5" t="n">
-        <v>48.74377351585415</v>
+        <v>53.50524988145118</v>
       </c>
       <c r="D5" t="n">
-        <v>34.70478134512475</v>
+        <v>29.42788743479815</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.39751000922872</v>
+        <v>13.76606630894878</v>
       </c>
       <c r="C6" t="n">
-        <v>27.97490083251287</v>
+        <v>44.1560664939088</v>
       </c>
       <c r="D6" t="n">
-        <v>32.00006641992479</v>
+        <v>30.75226508782709</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>17.78632315783946</v>
+        <v>22.27781890476862</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5916,7 +5916,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061760286306843</v>
+        <v>7.059912145385735</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20400268412665</v>
+        <v>66.18667636299126</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296320214730132</v>
+        <v>5.294934109039302</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.32794479094744</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C2" t="n">
-        <v>4.009457624143973</v>
+        <v>4.116468123906875</v>
       </c>
       <c r="D2" t="n">
-        <v>20.87784667851267</v>
+        <v>32.91211003717007</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.17705874412969</v>
+        <v>18.03470532701391</v>
       </c>
       <c r="C3" t="n">
-        <v>21.41682616814417</v>
+        <v>24.98057033456009</v>
       </c>
       <c r="D3" t="n">
-        <v>67.64241682260523</v>
+        <v>65.32058350206152</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.18459393059418</v>
+        <v>26.82723776624834</v>
       </c>
       <c r="C4" t="n">
-        <v>44.42702886028091</v>
+        <v>53.46303473016855</v>
       </c>
       <c r="D4" t="n">
-        <v>68.98250243890213</v>
+        <v>54.8796966673967</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.58711048933538</v>
+        <v>29.10881943091793</v>
       </c>
       <c r="C5" t="n">
-        <v>68.05965959691014</v>
+        <v>69.0904946863693</v>
       </c>
       <c r="D5" t="n">
-        <v>45.67581194008286</v>
+        <v>38.09181092477625</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.33337761328319</v>
+        <v>23.78872862160447</v>
       </c>
       <c r="C6" t="n">
-        <v>57.51961624411638</v>
+        <v>68.70957657712154</v>
       </c>
       <c r="D6" t="n">
-        <v>35.98498035146259</v>
+        <v>33.36862271964485</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>12.03720860177014</v>
       </c>
       <c r="C7" t="n">
-        <v>31.32069700858599</v>
+        <v>46.8912155979404</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>21.94696992843745</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286471553591353</v>
+        <v>7.283271616913003</v>
       </c>
       <c r="C21" t="n">
-        <v>75.59714236851029</v>
+        <v>75.56394302547241</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375662609392434</v>
+        <v>6.372862664798878</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.017311605777948</v>
+        <v>5.339725763398402</v>
       </c>
       <c r="C2" t="n">
-        <v>6.957645979997145</v>
+        <v>4.435536127787089</v>
       </c>
       <c r="D2" t="n">
-        <v>23.74651347032185</v>
+        <v>26.81840203691012</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.39795197758523</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="C3" t="n">
-        <v>17.84326452468578</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D3" t="n">
-        <v>68.64870821945821</v>
+        <v>76.49287237639024</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.17481751128071</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="C4" t="n">
-        <v>49.97881212779662</v>
+        <v>58.84890263566655</v>
       </c>
       <c r="D4" t="n">
-        <v>86.7354461747972</v>
+        <v>75.27452347541994</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.87658719336795</v>
+        <v>35.61289797155305</v>
       </c>
       <c r="C5" t="n">
-        <v>76.30634031258334</v>
+        <v>85.43659396207869</v>
       </c>
       <c r="D5" t="n">
-        <v>60.96653243372694</v>
+        <v>48.866491978885</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.47050349670826</v>
+        <v>32.36233132279187</v>
       </c>
       <c r="C6" t="n">
-        <v>85.33351045313277</v>
+        <v>91.8542787047401</v>
       </c>
       <c r="D6" t="n">
-        <v>42.54600025894403</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.80439552714341</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="C7" t="n">
-        <v>60.54536266860504</v>
+        <v>76.11588125795946</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>33.12907627980861</v>
+        <v>45.64635950895544</v>
       </c>
       <c r="D8" t="n">
         <v>34.46425315758427</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.07031028627404</v>
+        <v>28.17812260729194</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500279357377943</v>
+        <v>7.494134196735924</v>
       </c>
       <c r="C21" t="n">
-        <v>85.3156776901741</v>
+        <v>85.24577648787114</v>
       </c>
       <c r="D21" t="n">
-        <v>7.500279357377943</v>
+        <v>7.494134196735924</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_21_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497654078669</v>
+        <v>10.84497619107246</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907266867258</v>
+        <v>37.78907145010135</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.874778262212914</v>
+        <v>6.643486714638166</v>
       </c>
       <c r="C2" t="n">
-        <v>7.449501579824798</v>
+        <v>13.33704256219292</v>
       </c>
       <c r="D2" t="n">
-        <v>26.04478484596363</v>
+        <v>28.10056453865645</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4666743168825</v>
+        <v>19.97856578142259</v>
       </c>
       <c r="C3" t="n">
-        <v>18.20160243673586</v>
+        <v>25.52544031041707</v>
       </c>
       <c r="D3" t="n">
-        <v>79.8602670019568</v>
+        <v>78.24038328994955</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.15303913533804</v>
+        <v>36.85873580824224</v>
       </c>
       <c r="C4" t="n">
-        <v>53.37369568908209</v>
+        <v>67.78280674431252</v>
       </c>
       <c r="D4" t="n">
-        <v>95.52896036173588</v>
+        <v>96.29472357104839</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.42975311921541</v>
+        <v>47.0502587260284</v>
       </c>
       <c r="C5" t="n">
-        <v>96.94758579437256</v>
+        <v>113.2936850700819</v>
       </c>
       <c r="D5" t="n">
-        <v>63.93631923907354</v>
+        <v>66.6852128109646</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.8151790563569</v>
+        <v>44.96109961139118</v>
       </c>
       <c r="C6" t="n">
-        <v>114.9184775206104</v>
+        <v>148.0858419608847</v>
       </c>
       <c r="D6" t="n">
-        <v>44.11581483803468</v>
+        <v>45.8466360406218</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.88341836956866</v>
+        <v>31.14103717870882</v>
       </c>
       <c r="C7" t="n">
-        <v>105.6998665777328</v>
+        <v>147.9199265988669</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.27246819789088</v>
+        <v>15.93867397844697</v>
       </c>
       <c r="C8" t="n">
-        <v>73.51817683252239</v>
+        <v>99.30378028456487</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>43.04374634499714</v>
+        <v>50.36562072326985</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.691726952932148</v>
+        <v>7.645782771168984</v>
       </c>
       <c r="C21" t="n">
-        <v>94.22365517341882</v>
+        <v>92.70511610042394</v>
       </c>
       <c r="D21" t="n">
-        <v>8.653192822048668</v>
+        <v>7.645782771168984</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.219371706403543</v>
+        <v>6.598326320242812</v>
       </c>
       <c r="C2" t="n">
-        <v>9.371763584740052</v>
+        <v>12.5437904171615</v>
       </c>
       <c r="D2" t="n">
-        <v>25.80131141531043</v>
+        <v>29.30516897176729</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.99190933865455</v>
+        <v>20.84250376115979</v>
       </c>
       <c r="C3" t="n">
-        <v>23.75829444277281</v>
+        <v>38.34706532788041</v>
       </c>
       <c r="D3" t="n">
-        <v>81.34270603536947</v>
+        <v>81.0727254167016</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.34447993766616</v>
+        <v>37.16504109196725</v>
       </c>
       <c r="C4" t="n">
-        <v>49.28962523941536</v>
+        <v>65.71524607916875</v>
       </c>
       <c r="D4" t="n">
-        <v>110.0018850177424</v>
+        <v>108.8915283642392</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.28940425523712</v>
+        <v>50.31456984264904</v>
       </c>
       <c r="C5" t="n">
-        <v>96.67760517570468</v>
+        <v>117.3679380427062</v>
       </c>
       <c r="D5" t="n">
-        <v>81.53414683769762</v>
+        <v>82.83496254582464</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.85921883432777</v>
+        <v>52.93092747446678</v>
       </c>
       <c r="C6" t="n">
-        <v>134.0782657166912</v>
+        <v>162.9789546343088</v>
       </c>
       <c r="D6" t="n">
-        <v>52.40765594810324</v>
+        <v>53.93721887131977</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.68675003354981</v>
+        <v>40.90255460203486</v>
       </c>
       <c r="C7" t="n">
-        <v>134.026233088366</v>
+        <v>176.9050458190497</v>
       </c>
       <c r="D7" t="n">
-        <v>42.4596064609703</v>
+        <v>42.57937968088841</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.78283813537898</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="C8" t="n">
-        <v>105.9796646734432</v>
+        <v>143.1977201414398</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.09218647320796</v>
+        <v>11.20468654856884</v>
       </c>
       <c r="C9" t="n">
-        <v>65.56405693271472</v>
+        <v>81.7609305573786</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>40.9977841293468</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.874950570800553</v>
+        <v>7.81564195874341</v>
       </c>
       <c r="C21" t="n">
-        <v>103.3587262417573</v>
+        <v>100.6263902188214</v>
       </c>
       <c r="D21" t="n">
-        <v>9.843688213500691</v>
+        <v>8.792597203586336</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.497206306705391</v>
+        <v>8.517643082045327</v>
       </c>
       <c r="C2" t="n">
-        <v>14.90685714128357</v>
+        <v>13.00619358586174</v>
       </c>
       <c r="D2" t="n">
-        <v>36.56224800155971</v>
+        <v>40.01603642509999</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.57114048416017</v>
+        <v>20.86213871524472</v>
       </c>
       <c r="C3" t="n">
-        <v>29.55551463635023</v>
+        <v>42.55876297909924</v>
       </c>
       <c r="D3" t="n">
-        <v>82.10356050616076</v>
+        <v>83.7381704337317</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.8422260237193</v>
+        <v>37.19056653227767</v>
       </c>
       <c r="C4" t="n">
-        <v>53.29711936815084</v>
+        <v>77.73772846537518</v>
       </c>
       <c r="D4" t="n">
-        <v>122.2413336465873</v>
+        <v>120.2503493023748</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.17926858591223</v>
+        <v>51.98354093986863</v>
       </c>
       <c r="C5" t="n">
-        <v>92.89787651435444</v>
+        <v>118.5460352878024</v>
       </c>
       <c r="D5" t="n">
-        <v>96.97212948697872</v>
+        <v>96.53034302006766</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.97747052719389</v>
+        <v>59.16993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>143.1751399442421</v>
+        <v>171.3110474002515</v>
       </c>
       <c r="D6" t="n">
-        <v>63.3963580017378</v>
+        <v>64.24164277509429</v>
       </c>
     </row>
     <row r="7">
@@ -1472,10 +1472,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.59178254814513</v>
+        <v>49.34656660626167</v>
       </c>
       <c r="C7" t="n">
-        <v>159.5978155408827</v>
+        <v>200.1410504831632</v>
       </c>
       <c r="D7" t="n">
         <v>46.47200932822701</v>
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="C8" t="n">
-        <v>138.357703959503</v>
+        <v>180.1654299448534</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.30624853046277</v>
+        <v>16.08593613408398</v>
       </c>
       <c r="C9" t="n">
-        <v>93.63124204942677</v>
+        <v>121.0328022226595</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>56.51430659496764</v>
+        <v>64.34374453633596</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>39.44858625204532</v>
+        <v>39.626282586514</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.043306250684251</v>
+        <v>7.969166347974666</v>
       </c>
       <c r="C21" t="n">
-        <v>111.600874228244</v>
+        <v>107.583745697658</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05954609469084</v>
+        <v>9.961457934968333</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.039711876526377</v>
+        <v>7.81765696891735</v>
       </c>
       <c r="C2" t="n">
-        <v>10.01677182643021</v>
+        <v>9.155779089805753</v>
       </c>
       <c r="D2" t="n">
-        <v>29.87949137875167</v>
+        <v>32.81589876215389</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.92028281397354</v>
+        <v>24.98057033456009</v>
       </c>
       <c r="C3" t="n">
-        <v>46.17650326924873</v>
+        <v>60.01423716060751</v>
       </c>
       <c r="D3" t="n">
-        <v>89.65810909033996</v>
+        <v>90.57604319381073</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.13881164139307</v>
+        <v>24.9766433437431</v>
       </c>
       <c r="C4" t="n">
-        <v>76.04028668473245</v>
+        <v>100.2128786586974</v>
       </c>
       <c r="D4" t="n">
-        <v>115.3367020426195</v>
+        <v>113.6647857022872</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.40963513904496</v>
+        <v>33.33033455917922</v>
       </c>
       <c r="C5" t="n">
-        <v>85.53476873250337</v>
+        <v>102.34719816773</v>
       </c>
       <c r="D5" t="n">
-        <v>64.86897955810801</v>
+        <v>63.3963580017378</v>
       </c>
     </row>
     <row r="6">
@@ -1769,10 +1769,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.90068891761761</v>
+        <v>30.63151012020474</v>
       </c>
       <c r="C6" t="n">
-        <v>105.0970734873253</v>
+        <v>131.8241729877405</v>
       </c>
       <c r="D6" t="n">
         <v>30.59125846433062</v>
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="C7" t="n">
-        <v>97.25585457350601</v>
+        <v>126.6601800634022</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>69.01195487002953</v>
+        <v>89.20650514638642</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>43.15468383557703</v>
+        <v>49.03437083631118</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>27.8983245115816</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.745367491701582</v>
+        <v>4.629922173227958</v>
       </c>
       <c r="C2" t="n">
-        <v>4.300054944601029</v>
+        <v>4.201880174176349</v>
       </c>
       <c r="D2" t="n">
-        <v>21.86646661668921</v>
+        <v>22.33083328079795</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.14961086613979</v>
+        <v>26.66426764734337</v>
       </c>
       <c r="C3" t="n">
-        <v>43.44233591292136</v>
+        <v>49.05302404269188</v>
       </c>
       <c r="D3" t="n">
-        <v>92.61807841864409</v>
+        <v>94.9104593080604</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.32346232524949</v>
+        <v>34.089225534562</v>
       </c>
       <c r="C4" t="n">
-        <v>98.0815043927776</v>
+        <v>125.6617426481832</v>
       </c>
       <c r="D4" t="n">
-        <v>132.132441766874</v>
+        <v>129.9244911800229</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.62485887045326</v>
+        <v>36.49647090537518</v>
       </c>
       <c r="C5" t="n">
-        <v>112.9009859883832</v>
+        <v>140.6844460185679</v>
       </c>
       <c r="D5" t="n">
-        <v>83.71853547964676</v>
+        <v>80.55239913345081</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.57617239586842</v>
+        <v>36.02523200733671</v>
       </c>
       <c r="C6" t="n">
-        <v>122.6065437925672</v>
+        <v>150.3801863457094</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>37.43403996293088</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.82246789644735</v>
+        <v>19.46314823669301</v>
       </c>
       <c r="C7" t="n">
-        <v>121.9890244865959</v>
+        <v>155.4656394537079</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>89.70719647555229</v>
+        <v>114.8252114887069</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>49.47812079863073</v>
+        <v>53.13905798776709</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.463605900582747</v>
+        <v>4.656429361242622</v>
       </c>
       <c r="C2" t="n">
-        <v>9.116509181635882</v>
+        <v>8.629562320329464</v>
       </c>
       <c r="D2" t="n">
-        <v>19.20200334736336</v>
+        <v>29.89029060349839</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.87762569433442</v>
+        <v>21.22047662729481</v>
       </c>
       <c r="C3" t="n">
-        <v>28.96155727528091</v>
+        <v>32.41730919422968</v>
       </c>
       <c r="D3" t="n">
-        <v>89.54029936583034</v>
+        <v>91.71977926925825</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.84972015245478</v>
+        <v>41.91277298970483</v>
       </c>
       <c r="C4" t="n">
-        <v>104.3990508696058</v>
+        <v>123.9260127070749</v>
       </c>
       <c r="D4" t="n">
-        <v>145.8396032135679</v>
+        <v>142.6744486150762</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.15977250054753</v>
+        <v>42.90237467558562</v>
       </c>
       <c r="C5" t="n">
-        <v>146.1576894697439</v>
+        <v>184.6667431688251</v>
       </c>
       <c r="D5" t="n">
-        <v>106.519625910779</v>
+        <v>104.0898003427681</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.72838434775569</v>
+        <v>41.74096714146165</v>
       </c>
       <c r="C6" t="n">
-        <v>149.6154048841012</v>
+        <v>182.9035242919978</v>
       </c>
       <c r="D6" t="n">
-        <v>53.01143078621504</v>
+        <v>50.55607977789376</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.68568617038755</v>
+        <v>28.44613973055133</v>
       </c>
       <c r="C7" t="n">
-        <v>149.7764115075976</v>
+        <v>184.9897381635222</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>123.5873097491097</v>
+        <v>154.7970692671158</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>76.99061846244334</v>
+        <v>88.63905497333174</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>43.84485247166256</v>
+        <v>44.98367980858886</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
         <v>19.0517959486136</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.076396394482004</v>
+        <v>2.824488145118073</v>
       </c>
       <c r="C2" t="n">
-        <v>4.172427743048944</v>
+        <v>4.242131830050467</v>
       </c>
       <c r="D2" t="n">
-        <v>13.2506487642192</v>
+        <v>20.87490143539993</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.11677122354314</v>
+        <v>21.11739311834889</v>
       </c>
       <c r="C3" t="n">
-        <v>33.74757733348411</v>
+        <v>34.62133279026377</v>
       </c>
       <c r="D3" t="n">
-        <v>88.11185645615123</v>
+        <v>96.54506923563133</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.58919715793088</v>
+        <v>45.40975831223197</v>
       </c>
       <c r="C4" t="n">
-        <v>103.4673722982756</v>
+        <v>122.2540963667426</v>
       </c>
       <c r="D4" t="n">
-        <v>158.6788996897077</v>
+        <v>153.5738116276243</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.95146206079796</v>
+        <v>44.54680208019903</v>
       </c>
       <c r="C5" t="n">
-        <v>178.751713250738</v>
+        <v>224.157544572153</v>
       </c>
       <c r="D5" t="n">
-        <v>112.7782675253524</v>
+        <v>106.814150222053</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.93214590188251</v>
+        <v>33.85164259013428</v>
       </c>
       <c r="C6" t="n">
-        <v>184.6343454945849</v>
+        <v>216.2721470116427</v>
       </c>
       <c r="D6" t="n">
-        <v>51.92463607761381</v>
+        <v>49.10702016642546</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>158.8791762213741</v>
+        <v>195.1105752466026</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>95.46514676095984</v>
+        <v>109.3176068678823</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>19.01350778814797</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.56743447752142</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.04572553593887</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.794053966286422</v>
+        <v>3.662900684544849</v>
       </c>
       <c r="C2" t="n">
-        <v>8.229009256996765</v>
+        <v>6.884014902178635</v>
       </c>
       <c r="D2" t="n">
-        <v>16.38242394076652</v>
+        <v>24.04103778159589</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.2963899956913</v>
+        <v>15.73741569907637</v>
       </c>
       <c r="C3" t="n">
-        <v>24.71058971589222</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D3" t="n">
-        <v>79.21722225567514</v>
+        <v>91.20927046304992</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.00738062221102</v>
+        <v>42.83168884087984</v>
       </c>
       <c r="C4" t="n">
-        <v>94.75043443226816</v>
+        <v>106.3262216130423</v>
       </c>
       <c r="D4" t="n">
-        <v>165.3410396107266</v>
+        <v>163.8605640727224</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.10625940289948</v>
+        <v>54.09429850399926</v>
       </c>
       <c r="C5" t="n">
-        <v>185.8693841065274</v>
+        <v>224.1084571869407</v>
       </c>
       <c r="D5" t="n">
-        <v>139.972678932989</v>
+        <v>131.7259982173158</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.71329827929349</v>
+        <v>43.67304662341937</v>
       </c>
       <c r="C6" t="n">
-        <v>230.561484846955</v>
+        <v>279.6282533575063</v>
       </c>
       <c r="D6" t="n">
-        <v>69.11209313586272</v>
+        <v>64.20139111922018</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.40326162673396</v>
+        <v>18.08575620763474</v>
       </c>
       <c r="C7" t="n">
-        <v>208.465289267472</v>
+        <v>244.0978221931099</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>37.90822410408209</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>142.9473744768568</v>
+        <v>167.1474553865407</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>64.5656195174957</v>
+        <v>69.0031191406913</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.066578917439536</v>
+        <v>2.532909076956771</v>
       </c>
       <c r="C2" t="n">
-        <v>4.387430490278995</v>
+        <v>4.666246838285089</v>
       </c>
       <c r="D2" t="n">
-        <v>12.56244362354219</v>
+        <v>17.94831152904019</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.24101121362598</v>
+        <v>14.48568737616169</v>
       </c>
       <c r="C3" t="n">
-        <v>28.56885819358218</v>
+        <v>26.64463269325843</v>
       </c>
       <c r="D3" t="n">
-        <v>75.22641783791185</v>
+        <v>89.63847413625503</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.09373336245573</v>
+        <v>38.95182191369645</v>
       </c>
       <c r="C4" t="n">
-        <v>82.29401956078463</v>
+        <v>91.41936447175874</v>
       </c>
       <c r="D4" t="n">
-        <v>167.3575493952495</v>
+        <v>169.591025422411</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.20505606812991</v>
+        <v>58.51216317310991</v>
       </c>
       <c r="C5" t="n">
-        <v>187.7837921298087</v>
+        <v>221.4331946928681</v>
       </c>
       <c r="D5" t="n">
-        <v>158.8958659323463</v>
+        <v>149.5938064346078</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.20010627187966</v>
+        <v>50.47557646614552</v>
       </c>
       <c r="C6" t="n">
-        <v>263.0848227932433</v>
+        <v>316.0560019235842</v>
       </c>
       <c r="D6" t="n">
-        <v>83.48193428292329</v>
+        <v>76.35739119320418</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>16.04961146902685</v>
       </c>
       <c r="C7" t="n">
-        <v>255.5960513052486</v>
+        <v>297.7562247164236</v>
       </c>
       <c r="D7" t="n">
-        <v>45.6934833987593</v>
+        <v>42.4596064609703</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>180.9999154934632</v>
+        <v>207.3696588295325</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>74.77186865084555</v>
+        <v>72.88593131098743</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.837250865273282</v>
+        <v>3.205406254365836</v>
       </c>
       <c r="C2" t="n">
-        <v>5.358378969779091</v>
+        <v>5.264131190171397</v>
       </c>
       <c r="D2" t="n">
-        <v>17.56739341979242</v>
+        <v>16.21552683104457</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.184249773228911</v>
+        <v>11.71225011166445</v>
       </c>
       <c r="C3" t="n">
-        <v>23.25269437508571</v>
+        <v>22.92871763268426</v>
       </c>
       <c r="D3" t="n">
-        <v>68.91868883812609</v>
+        <v>84.05232969909068</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.84825537866502</v>
+        <v>33.47661496711199</v>
       </c>
       <c r="C4" t="n">
-        <v>77.18893149870122</v>
+        <v>79.92015361191584</v>
       </c>
       <c r="D4" t="n">
-        <v>166.3237690626776</v>
+        <v>172.9603835433861</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.72614311490671</v>
+        <v>58.16855147662353</v>
       </c>
       <c r="C5" t="n">
-        <v>171.9531103988289</v>
+        <v>199.2947839621026</v>
       </c>
       <c r="D5" t="n">
-        <v>175.9537322936346</v>
+        <v>167.068915570201</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.45798712292709</v>
+        <v>60.21647718768238</v>
       </c>
       <c r="C6" t="n">
-        <v>278.0986904342898</v>
+        <v>330.7076046617636</v>
       </c>
       <c r="D6" t="n">
-        <v>104.4932986492135</v>
+        <v>94.10837143369076</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.27888276793088</v>
+        <v>29.40432548989622</v>
       </c>
       <c r="C7" t="n">
-        <v>306.0205768907733</v>
+        <v>361.3558044929405</v>
       </c>
       <c r="D7" t="n">
-        <v>53.95783557310894</v>
+        <v>50.36463897556562</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>244.4208171878071</v>
+        <v>274.3788483828986</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>129.0203015444115</v>
+        <v>135.1218635263054</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>51.53193699591508</v>
+        <v>48.54251523648354</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.704355072301468</v>
+        <v>6.408849013323178</v>
       </c>
       <c r="C2" t="n">
-        <v>7.454410318346032</v>
+        <v>11.60818485501428</v>
       </c>
       <c r="D2" t="n">
-        <v>6.439283192154829</v>
+        <v>10.73442939823462</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.030254252382404</v>
+        <v>2.3699389580518</v>
       </c>
       <c r="C2" t="n">
-        <v>3.086614782151972</v>
+        <v>3.116067213279376</v>
       </c>
       <c r="D2" t="n">
-        <v>12.92863551722625</v>
+        <v>12.06371578978481</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.53691818323177</v>
+        <v>15.38889526406875</v>
       </c>
       <c r="C3" t="n">
-        <v>26.08994524035899</v>
+        <v>26.31083847381452</v>
       </c>
       <c r="D3" t="n">
-        <v>76.08053834060657</v>
+        <v>90.33551500627027</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.74311056331938</v>
+        <v>44.77162230447154</v>
       </c>
       <c r="C4" t="n">
-        <v>108.2278669161684</v>
+        <v>114.5837015534622</v>
       </c>
       <c r="D4" t="n">
-        <v>170.44612767281</v>
+        <v>174.4408590813902</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.53926689373454</v>
+        <v>34.45934441906305</v>
       </c>
       <c r="C5" t="n">
-        <v>243.5225180384214</v>
+        <v>288.3638444298944</v>
       </c>
       <c r="D5" t="n">
-        <v>157.8895745354933</v>
+        <v>147.3603304074463</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.04532462531138</v>
+        <v>18.23400011097601</v>
       </c>
       <c r="C6" t="n">
-        <v>256.0407830152724</v>
+        <v>293.1125580753363</v>
       </c>
       <c r="D6" t="n">
-        <v>82.11337798320324</v>
+        <v>74.34480839949822</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.28809404570082</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>171.8745705824891</v>
+        <v>192.9546572880766</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>95.04790398665493</v>
+        <v>99.5541259491478</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>39.2718716652809</v>
+        <v>37.05312185368311</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>19.41406085148067</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>18.64829764216817</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>14.9264920953685</v>
       </c>
       <c r="D11" t="n">
         <v>15.99267010218054</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.404922022506191</v>
+        <v>8.337001504463913</v>
       </c>
       <c r="C2" t="n">
-        <v>6.180101798233672</v>
+        <v>9.021279654323941</v>
       </c>
       <c r="D2" t="n">
-        <v>15.87976911619216</v>
+        <v>12.5899325592611</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.24025045009999</v>
+        <v>13.61193191938202</v>
       </c>
       <c r="C3" t="n">
-        <v>18.78083358224148</v>
+        <v>29.25117284803371</v>
       </c>
       <c r="D3" t="n">
-        <v>8.546113765468485</v>
+        <v>12.15403657857551</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39846600589229</v>
+        <v>13.39706722673332</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14491026614196</v>
+        <v>70.13758724583914</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576290118340269</v>
+        <v>1.576125556086273</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.123340357836604</v>
+        <v>5.338744015694155</v>
       </c>
       <c r="C2" t="n">
-        <v>3.867104207028186</v>
+        <v>6.15261286251476</v>
       </c>
       <c r="D2" t="n">
-        <v>20.28683456055609</v>
+        <v>23.82014454814036</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.00663555421825</v>
+        <v>22.68818944514379</v>
       </c>
       <c r="C3" t="n">
-        <v>22.10895829963817</v>
+        <v>32.96217917008666</v>
       </c>
       <c r="D3" t="n">
-        <v>19.81657741022187</v>
+        <v>19.7920337176157</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.51495988083984</v>
+        <v>15.81301027230337</v>
       </c>
       <c r="C4" t="n">
-        <v>29.1628155546515</v>
+        <v>45.11621574866217</v>
       </c>
       <c r="D4" t="n">
-        <v>19.55248727777947</v>
+        <v>21.44136986075034</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44140988897479</v>
+        <v>15.43703734530128</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14681306480672</v>
+        <v>86.1224188737861</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250823134521008</v>
+        <v>3.249902599010796</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.713370728088937</v>
+        <v>5.088398351111218</v>
       </c>
       <c r="C2" t="n">
-        <v>6.669012154948583</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="D2" t="n">
-        <v>19.21083907670159</v>
+        <v>25.25742318715769</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.33628179866693</v>
+        <v>20.29763378530281</v>
       </c>
       <c r="C3" t="n">
-        <v>17.82362957060084</v>
+        <v>27.5625667967292</v>
       </c>
       <c r="D3" t="n">
-        <v>31.44537896702533</v>
+        <v>34.25317740117121</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.07798434145878</v>
+        <v>31.2559016601057</v>
       </c>
       <c r="C4" t="n">
-        <v>44.59294422229862</v>
+        <v>66.77455185205106</v>
       </c>
       <c r="D4" t="n">
-        <v>25.09150782513998</v>
+        <v>26.54645792283375</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.23534171157875</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C5" t="n">
-        <v>32.98672286269284</v>
+        <v>49.01375413452202</v>
       </c>
       <c r="D5" t="n">
-        <v>29.47697482001049</v>
+        <v>30.65507206510666</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73506455830615</v>
+        <v>16.72303564217797</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0838938056675</v>
+        <v>102.0105174172856</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020519367491844</v>
+        <v>4.180758910544492</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.014767273292708</v>
+        <v>5.835508354043041</v>
       </c>
       <c r="C2" t="n">
-        <v>7.067601722872788</v>
+        <v>6.191882770684633</v>
       </c>
       <c r="D2" t="n">
-        <v>25.64325003492669</v>
+        <v>24.27076674438964</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.23319828972101</v>
+        <v>18.6973850273805</v>
       </c>
       <c r="C3" t="n">
-        <v>22.46238747316702</v>
+        <v>30.09056713516474</v>
       </c>
       <c r="D3" t="n">
-        <v>39.04901493641688</v>
+        <v>45.82798283424111</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.15830772675777</v>
+        <v>35.5952265128766</v>
       </c>
       <c r="C4" t="n">
-        <v>44.59294422229862</v>
+        <v>67.96148482648545</v>
       </c>
       <c r="D4" t="n">
-        <v>34.66354794154638</v>
+        <v>37.13951565165684</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.05344064885261</v>
+        <v>29.74695543867836</v>
       </c>
       <c r="C5" t="n">
-        <v>59.32210502911353</v>
+        <v>87.91550691530188</v>
       </c>
       <c r="D5" t="n">
-        <v>31.53864499892879</v>
+        <v>33.23215978875454</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.67927160034756</v>
+        <v>12.15600007398401</v>
       </c>
       <c r="C6" t="n">
-        <v>33.2881194078966</v>
+        <v>46.12839763174064</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>37.55479493055324</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06210526259669</v>
+        <v>18.03600369278852</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8337343321784</v>
+        <v>117.6634526624775</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880802004798739</v>
+        <v>6.012001230929505</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.69119144151876</v>
+        <v>7.068583470577035</v>
       </c>
       <c r="C2" t="n">
-        <v>6.548257187326225</v>
+        <v>7.290458451736814</v>
       </c>
       <c r="D2" t="n">
-        <v>33.81531792507713</v>
+        <v>36.5180693548686</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.91765636603028</v>
+        <v>17.18549356284042</v>
       </c>
       <c r="C3" t="n">
-        <v>23.78774687390022</v>
+        <v>25.03456645829367</v>
       </c>
       <c r="D3" t="n">
-        <v>46.89808783187013</v>
+        <v>50.3243873196915</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.32199755145973</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="C4" t="n">
-        <v>42.42328179591317</v>
+        <v>59.47427592327178</v>
       </c>
       <c r="D4" t="n">
-        <v>39.96007680595792</v>
+        <v>43.41877396801944</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.67837196810132</v>
+        <v>25.10819753611218</v>
       </c>
       <c r="C5" t="n">
-        <v>53.50524988145118</v>
+        <v>79.93880681829654</v>
       </c>
       <c r="D5" t="n">
-        <v>29.42788743479815</v>
+        <v>31.44047022850411</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.76606630894878</v>
+        <v>14.04782790006761</v>
       </c>
       <c r="C6" t="n">
-        <v>44.1560664939088</v>
+        <v>62.71207985187777</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>22.27781890476862</v>
+        <v>28.02693346083794</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.059912145385735</v>
+        <v>7.04320636162615</v>
       </c>
       <c r="C21" t="n">
-        <v>66.18667636299126</v>
+        <v>66.03005964024516</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294934109039302</v>
+        <v>4.402003976016344</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.591053175685585</v>
+        <v>5.325981295538947</v>
       </c>
       <c r="C2" t="n">
-        <v>4.116468123906875</v>
+        <v>7.6026542216873</v>
       </c>
       <c r="D2" t="n">
-        <v>32.91211003717007</v>
+        <v>27.0864191601695</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.03470532701391</v>
+        <v>21.5935407549086</v>
       </c>
       <c r="C3" t="n">
-        <v>24.98057033456009</v>
+        <v>27.20913762320035</v>
       </c>
       <c r="D3" t="n">
-        <v>65.32058350206152</v>
+        <v>68.84014902178635</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.82723776624834</v>
+        <v>30.5029011709484</v>
       </c>
       <c r="C4" t="n">
-        <v>53.46303473016855</v>
+        <v>61.56736202872597</v>
       </c>
       <c r="D4" t="n">
-        <v>54.8796966673967</v>
+        <v>59.71676760622073</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.10881943091793</v>
+        <v>33.37942194439156</v>
       </c>
       <c r="C5" t="n">
-        <v>69.0904946863693</v>
+        <v>98.10113934686255</v>
       </c>
       <c r="D5" t="n">
-        <v>38.09181092477625</v>
+        <v>40.15348110369455</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.78872862160447</v>
+        <v>25.1170332654504</v>
       </c>
       <c r="C6" t="n">
-        <v>68.70957657712154</v>
+        <v>100.0253648471863</v>
       </c>
       <c r="D6" t="n">
-        <v>33.36862271964485</v>
+        <v>33.97239755775664</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.03720860177014</v>
+        <v>11.97732199181109</v>
       </c>
       <c r="C7" t="n">
-        <v>46.8912155979404</v>
+        <v>63.83912621635309</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>22.96406055003713</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.283271616913003</v>
+        <v>7.258363209230467</v>
       </c>
       <c r="C21" t="n">
-        <v>75.56394302547241</v>
+        <v>75.30551829576611</v>
       </c>
       <c r="D21" t="n">
-        <v>6.372862664798878</v>
+        <v>5.44377240692285</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.339725763398402</v>
+        <v>5.899321954819084</v>
       </c>
       <c r="C2" t="n">
-        <v>4.435536127787089</v>
+        <v>5.944482349214438</v>
       </c>
       <c r="D2" t="n">
-        <v>26.81840203691012</v>
+        <v>27.6401248653647</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.79065105928395</v>
+        <v>19.7625812864883</v>
       </c>
       <c r="C3" t="n">
-        <v>19.54659679155399</v>
+        <v>28.56394945506095</v>
       </c>
       <c r="D3" t="n">
-        <v>76.49287237639024</v>
+        <v>74.11213419359171</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.46010518258904</v>
+        <v>36.51414236405162</v>
       </c>
       <c r="C4" t="n">
-        <v>58.84890263566655</v>
+        <v>65.30683903420207</v>
       </c>
       <c r="D4" t="n">
-        <v>75.27452347541994</v>
+        <v>79.07781408167207</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.61289797155305</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="C5" t="n">
-        <v>85.43659396207869</v>
+        <v>105.8324025178062</v>
       </c>
       <c r="D5" t="n">
-        <v>48.866491978885</v>
+        <v>52.54804586981054</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.36233132279187</v>
+        <v>35.46170882509904</v>
       </c>
       <c r="C6" t="n">
-        <v>91.8542787047401</v>
+        <v>130.4153650321463</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="C7" t="n">
-        <v>76.11588125795946</v>
+        <v>107.0772586067911</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>45.64635950895544</v>
+        <v>58.4974369575462</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>28.17812260729194</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.494134196735924</v>
+        <v>7.459678097350572</v>
       </c>
       <c r="C21" t="n">
-        <v>85.24577648787114</v>
+        <v>83.92137859519394</v>
       </c>
       <c r="D21" t="n">
-        <v>7.494134196735924</v>
+        <v>6.52721833518175</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_21_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497619107246</v>
+        <v>10.84497625899459</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907145010135</v>
+        <v>37.78907168677446</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.643486714638166</v>
+        <v>0.9709484795000954</v>
       </c>
       <c r="C2" t="n">
-        <v>13.33704256219292</v>
+        <v>4.861614631430205</v>
       </c>
       <c r="D2" t="n">
-        <v>28.10056453865645</v>
+        <v>21.02020009562846</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.97856578142259</v>
+        <v>7.932521450314228</v>
       </c>
       <c r="C3" t="n">
-        <v>25.52544031041707</v>
+        <v>50.27529993447916</v>
       </c>
       <c r="D3" t="n">
-        <v>78.24038328994955</v>
+        <v>77.55806863549803</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.85873580824224</v>
+        <v>14.2049075327471</v>
       </c>
       <c r="C4" t="n">
-        <v>67.78280674431252</v>
+        <v>152.4251668136555</v>
       </c>
       <c r="D4" t="n">
-        <v>96.29472357104839</v>
+        <v>76.0913375653533</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.0502587260284</v>
+        <v>14.25988540418492</v>
       </c>
       <c r="C5" t="n">
-        <v>113.2936850700819</v>
+        <v>208.0814259151115</v>
       </c>
       <c r="D5" t="n">
-        <v>66.6852128109646</v>
+        <v>43.6632291463769</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.96109961139118</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>148.0858419608847</v>
+        <v>136.2518551338936</v>
       </c>
       <c r="D6" t="n">
-        <v>45.8466360406218</v>
+        <v>28.77993394999525</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.14103717870882</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>147.9199265988669</v>
+        <v>60.7250224984822</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62686342359076</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.93867397844697</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>99.30378028456487</v>
+        <v>30.12492830481337</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>50.36562072326985</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.38218726105505</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.645782771168984</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.70511610042394</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.645782771168984</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.598326320242812</v>
+        <v>0.9081166264282996</v>
       </c>
       <c r="C2" t="n">
-        <v>12.5437904171615</v>
+        <v>6.31263773830699</v>
       </c>
       <c r="D2" t="n">
-        <v>29.30516897176729</v>
+        <v>18.47452829851648</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.84250376115979</v>
+        <v>5.625414345334224</v>
       </c>
       <c r="C3" t="n">
-        <v>38.34706532788041</v>
+        <v>33.472687976295</v>
       </c>
       <c r="D3" t="n">
-        <v>81.0727254167016</v>
+        <v>76.18362184955248</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.16504109196725</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="C4" t="n">
-        <v>65.71524607916875</v>
+        <v>138.4117000832366</v>
       </c>
       <c r="D4" t="n">
-        <v>108.8915283642392</v>
+        <v>95.46514676095984</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.31456984264904</v>
+        <v>17.59782759862408</v>
       </c>
       <c r="C5" t="n">
-        <v>117.3679380427062</v>
+        <v>244.5533531278805</v>
       </c>
       <c r="D5" t="n">
-        <v>82.83496254582464</v>
+        <v>59.07666810305183</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.93092747446678</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="C6" t="n">
-        <v>162.9789546343088</v>
+        <v>230.6822398145773</v>
       </c>
       <c r="D6" t="n">
-        <v>53.93721887131977</v>
+        <v>34.93843729873549</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.90255460203486</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>176.9050458190497</v>
+        <v>123.9053960052857</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.86628669023996</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>143.1977201414398</v>
+        <v>52.82293522699963</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.20468654856884</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>81.7609305573786</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
         <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.84931924182727</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>27.9631198600619</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>43.93222801734051</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.81564195874341</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6263902188214</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.792597203586336</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.517643082045327</v>
+        <v>0.5095270585040946</v>
       </c>
       <c r="C2" t="n">
-        <v>13.00619358586174</v>
+        <v>2.91480893390878</v>
       </c>
       <c r="D2" t="n">
-        <v>40.01603642509999</v>
+        <v>12.74013995801086</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.86213871524472</v>
+        <v>5.159084185816988</v>
       </c>
       <c r="C3" t="n">
-        <v>42.55876297909924</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="D3" t="n">
-        <v>83.7381704337317</v>
+        <v>76.16398689546754</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.19056653227767</v>
+        <v>15.94063747385546</v>
       </c>
       <c r="C4" t="n">
-        <v>77.73772846537518</v>
+        <v>131.5453566397344</v>
       </c>
       <c r="D4" t="n">
-        <v>120.2503493023748</v>
+        <v>107.2834256246829</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.98354093986863</v>
+        <v>17.52419652080557</v>
       </c>
       <c r="C5" t="n">
-        <v>118.5460352878024</v>
+        <v>286.3267179435823</v>
       </c>
       <c r="D5" t="n">
-        <v>96.53034302006766</v>
+        <v>65.48257187326226</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.16993413495527</v>
+        <v>10.94845039776043</v>
       </c>
       <c r="C6" t="n">
-        <v>171.3110474002515</v>
+        <v>263.9703592224739</v>
       </c>
       <c r="D6" t="n">
-        <v>64.24164277509429</v>
+        <v>35.34095385747668</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.34656660626167</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>200.1410504831632</v>
+        <v>107.7958979262998</v>
       </c>
       <c r="D7" t="n">
-        <v>46.47200932822701</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.71045084717197</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>180.1654299448534</v>
+        <v>41.72427743048944</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>35.13184159647211</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.08593613408398</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>121.0328022226595</v>
+        <v>24.96093538047515</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>64.34374453633596</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.626282586514</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>37.98872741583033</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.969166347974666</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.583745697658</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.961457934968333</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.81765696891735</v>
+        <v>0.4290237467558561</v>
       </c>
       <c r="C2" t="n">
-        <v>9.155779089805753</v>
+        <v>3.531346492175777</v>
       </c>
       <c r="D2" t="n">
-        <v>32.81589876215389</v>
+        <v>10.98870205363455</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.98057033456009</v>
+        <v>3.470478134512474</v>
       </c>
       <c r="C3" t="n">
-        <v>60.01423716060751</v>
+        <v>21.18120671912493</v>
       </c>
       <c r="D3" t="n">
-        <v>90.57604319381073</v>
+        <v>69.35065782799468</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.9766433437431</v>
+        <v>13.26046624126167</v>
       </c>
       <c r="C4" t="n">
-        <v>100.2128786586974</v>
+        <v>106.5304251355256</v>
       </c>
       <c r="D4" t="n">
-        <v>113.6647857022872</v>
+        <v>119.8547049775634</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.33033455917922</v>
+        <v>20.39580855572749</v>
       </c>
       <c r="C5" t="n">
-        <v>102.34719816773</v>
+        <v>268.0662106445916</v>
       </c>
       <c r="D5" t="n">
-        <v>63.3963580017378</v>
+        <v>83.76762286485911</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.63151012020474</v>
+        <v>15.85915241440298</v>
       </c>
       <c r="C6" t="n">
-        <v>131.8241729877405</v>
+        <v>350.9541875664456</v>
       </c>
       <c r="D6" t="n">
-        <v>30.59125846433062</v>
+        <v>44.55858305264999</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>126.6601800634022</v>
+        <v>224.3352409066217</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>89.20650514638642</v>
+        <v>82.19682653806419</v>
       </c>
       <c r="D8" t="n">
-        <v>26.62008900065226</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03437083631118</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>26.95781021091316</v>
+        <v>40.15937158992001</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>31.31775176547326</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>22.93362637120549</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>45.33318199130072</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.629922173227958</v>
+        <v>0.3229949946972006</v>
       </c>
       <c r="C2" t="n">
-        <v>4.201880174176349</v>
+        <v>2.804853191033137</v>
       </c>
       <c r="D2" t="n">
-        <v>22.33083328079795</v>
+        <v>9.386489800303753</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.66426764734337</v>
+        <v>2.670353755551325</v>
       </c>
       <c r="C3" t="n">
-        <v>49.05302404269188</v>
+        <v>17.94634803363169</v>
       </c>
       <c r="D3" t="n">
-        <v>94.9104593080604</v>
+        <v>63.84796194569132</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.089225534562</v>
+        <v>11.00146477378976</v>
       </c>
       <c r="C4" t="n">
-        <v>125.6617426481832</v>
+        <v>86.13559832750241</v>
       </c>
       <c r="D4" t="n">
-        <v>129.9244911800229</v>
+        <v>125.4830645660103</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.49647090537518</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="C5" t="n">
-        <v>140.6844460185679</v>
+        <v>249.7075285751763</v>
       </c>
       <c r="D5" t="n">
-        <v>80.55239913345081</v>
+        <v>99.72102305886979</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.02523200733671</v>
+        <v>18.99878157258428</v>
       </c>
       <c r="C6" t="n">
-        <v>150.3801863457094</v>
+        <v>392.9769162990261</v>
       </c>
       <c r="D6" t="n">
-        <v>37.43403996293088</v>
+        <v>52.89067581859268</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.46314823669301</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>155.4656394537079</v>
+        <v>312.5482173763103</v>
       </c>
       <c r="D7" t="n">
-        <v>30.48228446915921</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>114.8252114887069</v>
+        <v>127.5928403824367</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>53.13905798776709</v>
+        <v>41.71249645803847</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.28621266575034</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>38.85168364786328</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.656429361242622</v>
+        <v>0.5635231822376692</v>
       </c>
       <c r="C2" t="n">
-        <v>8.629562320329464</v>
+        <v>6.361725123519331</v>
       </c>
       <c r="D2" t="n">
-        <v>29.89029060349839</v>
+        <v>12.42598069265188</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.22047662729481</v>
+        <v>1.934042977366216</v>
       </c>
       <c r="C3" t="n">
-        <v>32.41730919422968</v>
+        <v>14.69185439405352</v>
       </c>
       <c r="D3" t="n">
-        <v>91.71977926925825</v>
+        <v>57.73167374823369</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.91277298970483</v>
+        <v>8.308530821040756</v>
       </c>
       <c r="C4" t="n">
-        <v>123.9260127070749</v>
+        <v>67.66794226291564</v>
       </c>
       <c r="D4" t="n">
-        <v>142.6744486150762</v>
+        <v>127.4995743505333</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.90237467558562</v>
+        <v>19.75767254796706</v>
       </c>
       <c r="C5" t="n">
-        <v>184.6667431688251</v>
+        <v>210.609426253547</v>
       </c>
       <c r="D5" t="n">
-        <v>104.0898003427681</v>
+        <v>115.6989669454866</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.74096714146165</v>
+        <v>22.66168225712913</v>
       </c>
       <c r="C6" t="n">
-        <v>182.9035242919978</v>
+        <v>395.995790489585</v>
       </c>
       <c r="D6" t="n">
-        <v>50.55607977789376</v>
+        <v>66.01271563355554</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.44613973055133</v>
+        <v>11.91743538185203</v>
       </c>
       <c r="C7" t="n">
-        <v>184.9897381635222</v>
+        <v>413.756588207114</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>43.05847256056086</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>154.7970692671158</v>
+        <v>237.4111385794849</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>88.63905497333174</v>
+        <v>83.42499291607693</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98367980858886</v>
+        <v>37.29659528433633</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>9.675123625352315</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.824488145118073</v>
+        <v>0.4005530633326986</v>
       </c>
       <c r="C2" t="n">
-        <v>4.242131830050467</v>
+        <v>3.612831551628263</v>
       </c>
       <c r="D2" t="n">
-        <v>20.87490143539993</v>
+        <v>9.145961612763285</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.11739311834889</v>
+        <v>2.925608158655495</v>
       </c>
       <c r="C3" t="n">
-        <v>34.62133279026377</v>
+        <v>19.92947839621025</v>
       </c>
       <c r="D3" t="n">
-        <v>96.54506923563133</v>
+        <v>62.68949965468008</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.40975831223197</v>
+        <v>13.59229696529709</v>
       </c>
       <c r="C4" t="n">
-        <v>122.2540963667426</v>
+        <v>103.6843385409141</v>
       </c>
       <c r="D4" t="n">
-        <v>153.5738116276243</v>
+        <v>128.2653375598458</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.54680208019903</v>
+        <v>13.30268139254428</v>
       </c>
       <c r="C5" t="n">
-        <v>224.157544572153</v>
+        <v>324.7621405648449</v>
       </c>
       <c r="D5" t="n">
-        <v>106.814150222053</v>
+        <v>103.0098778680966</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.85164259013428</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>216.2721470116427</v>
+        <v>350.1491544489632</v>
       </c>
       <c r="D6" t="n">
-        <v>49.10702016642546</v>
+        <v>56.99634471775284</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.743445054022093</v>
+        <v>3.293763547748049</v>
       </c>
       <c r="C7" t="n">
-        <v>195.1105752466026</v>
+        <v>166.9638685658466</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>109.3176068678823</v>
+        <v>61.41813637768045</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>28.39999758845172</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.01350778814797</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.52848336452105</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>7.989462817160544</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.662900684544849</v>
+        <v>0.2346377013149877</v>
       </c>
       <c r="C2" t="n">
-        <v>6.884014902178635</v>
+        <v>2.220713307006285</v>
       </c>
       <c r="D2" t="n">
-        <v>24.04103778159589</v>
+        <v>7.249225048158447</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.73741569907637</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C3" t="n">
-        <v>25.75615102091507</v>
+        <v>17.0971362694582</v>
       </c>
       <c r="D3" t="n">
-        <v>91.20927046304992</v>
+        <v>56.56830271870122</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.83168884087984</v>
+        <v>9.201921231905354</v>
       </c>
       <c r="C4" t="n">
-        <v>106.3262216130423</v>
+        <v>74.38113306455534</v>
       </c>
       <c r="D4" t="n">
-        <v>163.8605640727224</v>
+        <v>124.2067925504895</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.09429850399926</v>
+        <v>12.78726384781471</v>
       </c>
       <c r="C5" t="n">
-        <v>224.1084571869407</v>
+        <v>239.6937019918588</v>
       </c>
       <c r="D5" t="n">
-        <v>131.7259982173158</v>
+        <v>107.9922474671492</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.67304662341937</v>
+        <v>7.084291433844984</v>
       </c>
       <c r="C6" t="n">
-        <v>279.6282533575063</v>
+        <v>344.2724126913418</v>
       </c>
       <c r="D6" t="n">
-        <v>64.20139111922018</v>
+        <v>60.09572222006002</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.08575620763474</v>
+        <v>2.515237618280328</v>
       </c>
       <c r="C7" t="n">
-        <v>244.0978221931099</v>
+        <v>216.7296414418216</v>
       </c>
       <c r="D7" t="n">
-        <v>37.90822410408209</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>167.1474553865407</v>
+        <v>75.18714792974197</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>25.45180923259856</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>69.0031191406913</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>15.65887588273663</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>12.26104707833841</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>7.804894248762142</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.532909076956771</v>
+        <v>0.1600248757922301</v>
       </c>
       <c r="C2" t="n">
-        <v>4.666246838285089</v>
+        <v>4.19500794024662</v>
       </c>
       <c r="D2" t="n">
-        <v>17.94831152904019</v>
+        <v>9.156760837509999</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.48568737616169</v>
+        <v>1.45298660228528</v>
       </c>
       <c r="C3" t="n">
-        <v>26.64463269325843</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="D3" t="n">
-        <v>89.63847413625503</v>
+        <v>49.74515617418589</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.95182191369645</v>
+        <v>6.649377200863647</v>
       </c>
       <c r="C4" t="n">
-        <v>91.41936447175874</v>
+        <v>57.31737621704153</v>
       </c>
       <c r="D4" t="n">
-        <v>169.591025422411</v>
+        <v>124.3727079125072</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.51216317310991</v>
+        <v>13.52357462599982</v>
       </c>
       <c r="C5" t="n">
-        <v>221.4331946928681</v>
+        <v>186.4584327290755</v>
       </c>
       <c r="D5" t="n">
-        <v>149.5938064346078</v>
+        <v>125.0255701358313</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.47557646614552</v>
+        <v>11.7132318593687</v>
       </c>
       <c r="C6" t="n">
-        <v>316.0560019235842</v>
+        <v>367.4976181307086</v>
       </c>
       <c r="D6" t="n">
-        <v>76.35739119320418</v>
+        <v>78.36997398691015</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.04961146902685</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>297.7562247164236</v>
+        <v>354.8281640074034</v>
       </c>
       <c r="D7" t="n">
-        <v>42.4596064609703</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>207.3696588295325</v>
+        <v>172.9054056719482</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>72.88593131098743</v>
+        <v>57.243745139223</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>23.20360698987336</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.205406254365836</v>
+        <v>0.3112140222462389</v>
       </c>
       <c r="C2" t="n">
-        <v>5.264131190171397</v>
+        <v>11.83791381780804</v>
       </c>
       <c r="D2" t="n">
-        <v>16.21552683104457</v>
+        <v>10.28478894968958</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.71225011166445</v>
+        <v>0.9915651812892785</v>
       </c>
       <c r="C3" t="n">
-        <v>22.92871763268426</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D3" t="n">
-        <v>84.05232969909068</v>
+        <v>45.86234400388975</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.47661496711199</v>
+        <v>4.773257338047992</v>
       </c>
       <c r="C4" t="n">
-        <v>79.92015361191584</v>
+        <v>44.36321525950487</v>
       </c>
       <c r="D4" t="n">
-        <v>172.9603835433861</v>
+        <v>121.3989941163436</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.16855147662353</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C5" t="n">
-        <v>199.2947839621026</v>
+        <v>146.3785827031994</v>
       </c>
       <c r="D5" t="n">
-        <v>167.068915570201</v>
+        <v>138.7454943026805</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.21647718768238</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="C6" t="n">
-        <v>330.7076046617636</v>
+        <v>336.7051013870074</v>
       </c>
       <c r="D6" t="n">
-        <v>94.10837143369076</v>
+        <v>94.79264958355078</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.40432548989622</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>361.3558044929405</v>
+        <v>437.4117991409409</v>
       </c>
       <c r="D7" t="n">
-        <v>50.36463897556562</v>
+        <v>50.72395863531995</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>3.171045084717197</v>
       </c>
       <c r="C8" t="n">
-        <v>274.3788483828986</v>
+        <v>305.1713651265998</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>135.1218635263054</v>
+        <v>124.2499894494763</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>48.54251523648354</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.408849013323178</v>
+        <v>4.534692645916017</v>
       </c>
       <c r="C2" t="n">
-        <v>11.60818485501428</v>
+        <v>19.79596070843268</v>
       </c>
       <c r="D2" t="n">
-        <v>10.73442939823462</v>
+        <v>7.777405313043232</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.3699389580518</v>
+        <v>0.1639518666092173</v>
       </c>
       <c r="C2" t="n">
-        <v>3.116067213279376</v>
+        <v>23.54034645243002</v>
       </c>
       <c r="D2" t="n">
-        <v>12.06371578978481</v>
+        <v>18.19669369821463</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.38889526406875</v>
+        <v>0.9915651812892785</v>
       </c>
       <c r="C3" t="n">
-        <v>26.31083847381452</v>
+        <v>28.52467954689108</v>
       </c>
       <c r="D3" t="n">
-        <v>90.33551500627027</v>
+        <v>43.59450680707962</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.77162230447154</v>
+        <v>3.445934441906304</v>
       </c>
       <c r="C4" t="n">
-        <v>114.5837015534622</v>
+        <v>39.98560224626834</v>
       </c>
       <c r="D4" t="n">
-        <v>174.4408590813902</v>
+        <v>117.3914999876081</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.45934441906305</v>
+        <v>10.11200135374215</v>
       </c>
       <c r="C5" t="n">
-        <v>288.3638444298944</v>
+        <v>118.1042488208913</v>
       </c>
       <c r="D5" t="n">
-        <v>147.3603304074463</v>
+        <v>145.9122525436822</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.23400011097601</v>
+        <v>15.17487426454295</v>
       </c>
       <c r="C6" t="n">
-        <v>293.1125580753363</v>
+        <v>292.4685315813504</v>
       </c>
       <c r="D6" t="n">
-        <v>74.34480839949822</v>
+        <v>111.3763318036879</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>192.9546572880766</v>
+        <v>462.0850824440717</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>61.20411537815465</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>99.5541259491478</v>
+        <v>415.3234575430919</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>37.05312185368311</v>
+        <v>226.2015432923947</v>
       </c>
       <c r="D9" t="n">
-        <v>19.41406085148067</v>
+        <v>25.18281036163492</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>81.99556825869361</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.9264920953685</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.337001504463913</v>
+        <v>4.07817996344125</v>
       </c>
       <c r="C2" t="n">
-        <v>9.021279654323941</v>
+        <v>20.0374706436774</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5899325592611</v>
+        <v>18.87213611873644</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.61193191938202</v>
+        <v>7.314020396638738</v>
       </c>
       <c r="C3" t="n">
-        <v>29.25117284803371</v>
+        <v>39.08337610606552</v>
       </c>
       <c r="D3" t="n">
-        <v>12.15403657857551</v>
+        <v>8.354672963140358</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39706722673332</v>
+        <v>11.6770916046361</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13758724583914</v>
+        <v>59.94240357046532</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576125556086273</v>
+        <v>0.7784727736424067</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.338744015694155</v>
+        <v>2.555489274154447</v>
       </c>
       <c r="C2" t="n">
-        <v>6.15261286251476</v>
+        <v>8.896597695884596</v>
       </c>
       <c r="D2" t="n">
-        <v>23.82014454814036</v>
+        <v>18.25363506506094</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.68818944514379</v>
+        <v>11.56989669454866</v>
       </c>
       <c r="C3" t="n">
-        <v>32.96217917008666</v>
+        <v>64.80025721881071</v>
       </c>
       <c r="D3" t="n">
-        <v>19.7920337176157</v>
+        <v>22.85999529338698</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.81301027230337</v>
+        <v>8.959429548956392</v>
       </c>
       <c r="C4" t="n">
-        <v>45.11621574866217</v>
+        <v>63.04783756673017</v>
       </c>
       <c r="D4" t="n">
-        <v>21.44136986075034</v>
+        <v>18.58252054598363</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43703734530128</v>
+        <v>13.62273879555909</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1224188737861</v>
+        <v>73.72305701126098</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249902599010796</v>
+        <v>1.602675152418717</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.088398351111218</v>
+        <v>1.780890335503714</v>
       </c>
       <c r="C2" t="n">
-        <v>8.266315669758143</v>
+        <v>11.98124898262807</v>
       </c>
       <c r="D2" t="n">
-        <v>25.25742318715769</v>
+        <v>25.77382247959151</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.29763378530281</v>
+        <v>10.04327901444487</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5625667967292</v>
+        <v>45.96542751283567</v>
       </c>
       <c r="D3" t="n">
-        <v>34.25317740117121</v>
+        <v>32.66765485881262</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.2559016601057</v>
+        <v>16.96165508627214</v>
       </c>
       <c r="C4" t="n">
-        <v>66.77455185205106</v>
+        <v>123.4665547814874</v>
       </c>
       <c r="D4" t="n">
-        <v>26.54645792283375</v>
+        <v>26.25291535926396</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.71992416684918</v>
+        <v>8.39394287131023</v>
       </c>
       <c r="C5" t="n">
-        <v>49.01375413452202</v>
+        <v>70.78400947619504</v>
       </c>
       <c r="D5" t="n">
-        <v>30.65507206510666</v>
+        <v>26.85079971115027</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.70768553050848</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72303564217797</v>
+        <v>14.82130930711075</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0105174172856</v>
+        <v>87.28104369742995</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180758910544492</v>
+        <v>2.470218217851791</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.835508354043041</v>
+        <v>1.276272015520853</v>
       </c>
       <c r="C2" t="n">
-        <v>6.191882770684633</v>
+        <v>7.148105034621026</v>
       </c>
       <c r="D2" t="n">
-        <v>24.27076674438964</v>
+        <v>33.20467085303562</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6973850273805</v>
+        <v>7.878525326580654</v>
       </c>
       <c r="C3" t="n">
-        <v>30.09056713516474</v>
+        <v>46.28940425523712</v>
       </c>
       <c r="D3" t="n">
-        <v>45.82798283424111</v>
+        <v>44.98858854711008</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.5952265128766</v>
+        <v>18.25068982194821</v>
       </c>
       <c r="C4" t="n">
-        <v>67.96148482648545</v>
+        <v>118.731585603905</v>
       </c>
       <c r="D4" t="n">
-        <v>37.13951565165684</v>
+        <v>35.90153179660161</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.74695543867836</v>
+        <v>17.10695374650068</v>
       </c>
       <c r="C5" t="n">
-        <v>87.91550691530188</v>
+        <v>157.3005259129452</v>
       </c>
       <c r="D5" t="n">
-        <v>33.23215978875454</v>
+        <v>30.33600406122645</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.15600007398401</v>
+        <v>7.969827863075609</v>
       </c>
       <c r="C6" t="n">
-        <v>46.12839763174064</v>
+        <v>64.16113946334606</v>
       </c>
       <c r="D6" t="n">
-        <v>37.55479493055324</v>
+        <v>33.24786775202249</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>17.78632315783946</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>25.2849121228766</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03600369278852</v>
+        <v>16.04078906112035</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6634526624775</v>
+        <v>100.4659946459643</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012001230929505</v>
+        <v>3.377008223393758</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.068583470577035</v>
+        <v>2.473022466997715</v>
       </c>
       <c r="C2" t="n">
-        <v>7.290458451736814</v>
+        <v>5.094288837336698</v>
       </c>
       <c r="D2" t="n">
-        <v>36.5180693548686</v>
+        <v>31.10176727053895</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18549356284042</v>
+        <v>6.003387211469246</v>
       </c>
       <c r="C3" t="n">
-        <v>25.03456645829367</v>
+        <v>36.1970378555799</v>
       </c>
       <c r="D3" t="n">
-        <v>50.3243873196915</v>
+        <v>59.32210502911352</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.03594911662541</v>
+        <v>16.69363796301277</v>
       </c>
       <c r="C4" t="n">
-        <v>59.47427592327178</v>
+        <v>115.9237871697591</v>
       </c>
       <c r="D4" t="n">
-        <v>43.41877396801944</v>
+        <v>48.81740459367264</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.10819753611218</v>
+        <v>21.86843011209771</v>
       </c>
       <c r="C5" t="n">
-        <v>79.93880681829654</v>
+        <v>188.7900835266616</v>
       </c>
       <c r="D5" t="n">
-        <v>31.44047022850411</v>
+        <v>35.41654843070369</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.04782790006761</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="C6" t="n">
-        <v>62.71207985187777</v>
+        <v>154.6468618683661</v>
       </c>
       <c r="D6" t="n">
-        <v>30.3497485290859</v>
+        <v>35.46170882509904</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>28.02693346083794</v>
+        <v>53.35896947351839</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.2754388031994</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.04320636162615</v>
+        <v>17.27341445806709</v>
       </c>
       <c r="C21" t="n">
-        <v>66.03005964024516</v>
+        <v>113.1408647003395</v>
       </c>
       <c r="D21" t="n">
-        <v>4.402003976016344</v>
+        <v>4.318353614516774</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.325981295538947</v>
+        <v>1.826050729899067</v>
       </c>
       <c r="C2" t="n">
-        <v>7.6026542216873</v>
+        <v>17.41129553481718</v>
       </c>
       <c r="D2" t="n">
-        <v>27.0864191601695</v>
+        <v>36.87444377151019</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.5935407549086</v>
+        <v>7.024404823885928</v>
       </c>
       <c r="C3" t="n">
-        <v>27.20913762320035</v>
+        <v>27.84727363096077</v>
       </c>
       <c r="D3" t="n">
-        <v>68.84014902178635</v>
+        <v>67.74059159302992</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.5029011709484</v>
+        <v>13.98794129010856</v>
       </c>
       <c r="C4" t="n">
-        <v>61.56736202872597</v>
+        <v>102.3442529246172</v>
       </c>
       <c r="D4" t="n">
-        <v>59.71676760622073</v>
+        <v>63.04783756673017</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.37942194439156</v>
+        <v>23.39013905368026</v>
       </c>
       <c r="C5" t="n">
-        <v>98.10113934686255</v>
+        <v>200.2519879737432</v>
       </c>
       <c r="D5" t="n">
-        <v>40.15348110369455</v>
+        <v>43.31961744989052</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.1170332654504</v>
+        <v>21.17237098978672</v>
       </c>
       <c r="C6" t="n">
-        <v>100.0253648471863</v>
+        <v>218.6067430523415</v>
       </c>
       <c r="D6" t="n">
-        <v>33.97239755775664</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.97732199181109</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>63.83912621635309</v>
+        <v>129.5347373414369</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>38.44720359371359</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>45.31256528951153</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.96406055003713</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>43.13308538608361</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>46.91183229972957</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.2611134982632</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.26022956155019</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.40561033723673</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>28.30869505195678</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.258363209230467</v>
+        <v>17.63182354146792</v>
       </c>
       <c r="C21" t="n">
-        <v>75.30551829576611</v>
+        <v>125.1859471444222</v>
       </c>
       <c r="D21" t="n">
-        <v>5.44377240692285</v>
+        <v>5.289547062440374</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.899321954819084</v>
+        <v>1.735729941108361</v>
       </c>
       <c r="C2" t="n">
-        <v>5.944482349214438</v>
+        <v>11.56106096521044</v>
       </c>
       <c r="D2" t="n">
-        <v>27.6401248653647</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.7625812864883</v>
+        <v>9.189158511750145</v>
       </c>
       <c r="C3" t="n">
-        <v>28.56394945506095</v>
+        <v>53.68687320673683</v>
       </c>
       <c r="D3" t="n">
-        <v>74.11213419359171</v>
+        <v>71.11780369563894</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.51414236405162</v>
+        <v>11.23119373658351</v>
       </c>
       <c r="C4" t="n">
-        <v>65.30683903420207</v>
+        <v>158.9086286525015</v>
       </c>
       <c r="D4" t="n">
-        <v>79.07781408167207</v>
+        <v>57.11317269455819</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.25165587411923</v>
+        <v>11.92823460659875</v>
       </c>
       <c r="C5" t="n">
-        <v>105.8324025178062</v>
+        <v>130.6215320500382</v>
       </c>
       <c r="D5" t="n">
-        <v>52.54804586981054</v>
+        <v>34.68023765251858</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.46170882509904</v>
+        <v>7.567311304334416</v>
       </c>
       <c r="C6" t="n">
-        <v>130.4153650321463</v>
+        <v>85.29325879725866</v>
       </c>
       <c r="D6" t="n">
-        <v>38.64158963915446</v>
+        <v>25.318291544821</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>107.0772586067911</v>
+        <v>31.85967649821749</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>58.4974369575462</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>30.17499743772996</v>
+        <v>25.29374785221481</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.29905750136355</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>29.75873641112932</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.459678097350572</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.92137859519394</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.52721833518175</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
